--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:14</t>
+    <t xml:space="preserve">2026-09-24 01:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -944,7 +944,7 @@
         <v>-0.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.05</v>
@@ -967,7 +967,7 @@
         <v>-0.33</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.28</v>
@@ -990,7 +990,7 @@
         <v>-0.63</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.26</v>
@@ -1013,7 +1013,7 @@
         <v>-0.32</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.42</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:04</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_los_rios.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
